--- a/outputs/reports/gradient_boosting_v2/evaluation.xlsx
+++ b/outputs/reports/gradient_boosting_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9885835143652664</v>
+        <v>0.9961099585062241</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2108825121819166</v>
+        <v>0.5545454545454546</v>
       </c>
       <c r="D2" t="n">
-        <v>0.917550058892815</v>
+        <v>0.3765432098765432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3429451904028175</v>
+        <v>0.4485294117647059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9888149185580262</v>
+        <v>0.9987238918693682</v>
       </c>
       <c r="G2" t="n">
-        <v>257700</v>
+        <v>38349</v>
       </c>
       <c r="H2" t="n">
-        <v>2915</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="J2" t="n">
-        <v>779</v>
+        <v>61</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9845880859822671</v>
+        <v>0.8887462952995879</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7453264652585436</v>
+        <v>0.3880114589120946</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2948374760994264</v>
+        <v>0.1917098445595855</v>
       </c>
       <c r="E2" t="n">
-        <v>90.8002189056071</v>
+        <v>45.63167658159023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9081272084805654</v>
+        <v>0.4567901234567901</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06180204986997093</v>
+        <v>0.05549792531120332</v>
       </c>
       <c r="I2" t="n">
-        <v>19.03299312980221</v>
+        <v>13.20987654320988</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9517078916372202</v>
+        <v>0.6604938271604939</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03113167858645351</v>
+        <v>0.03137966804979253</v>
       </c>
       <c r="M2" t="n">
-        <v>9.587530282601273</v>
+        <v>7.469135802469136</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9587750294464076</v>
+        <v>0.7469135802469136</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>215820</v>
+        <v>37270</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001390047261606895</v>
+        <v>0.001797692514086397</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24596</v>
+        <v>766</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002845991218084242</v>
+        <v>0.02219321148825065</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9667</v>
+        <v>239</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008275576704251578</v>
+        <v>0.02510460251046025</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5087</v>
+        <v>117</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001965795164143896</v>
+        <v>0.04273504273504274</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2592</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005787037037037037</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1444</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007617728531855956</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>820</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03048780487804878</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>406</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0960591133004926</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3252032520325203</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>786</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>624</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7938931297709924</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
